--- a/Experiments data/Cardinality Skewness/Skewness_email_Graph.xlsx
+++ b/Experiments data/Cardinality Skewness/Skewness_email_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\SISR Script\Experiments data\Cardinality Skewness\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Cardinality Skewness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABF5703-1B7A-437C-80BF-2FCEC69A55BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9284ECC-9D6B-4823-9810-82B7420064B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="34">
   <si>
     <t>KaHIP</t>
   </si>
@@ -120,6 +120,24 @@
   </si>
   <si>
     <t>Deep Multilevel, ε= 0</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 50</t>
+  </si>
+  <si>
+    <t>108, 184, 311, 530</t>
+  </si>
+  <si>
+    <t>447, 312, 220, 153</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 10</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 50</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε= 0</t>
   </si>
 </sst>
 </file>
@@ -309,13 +327,17 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -329,10 +351,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -688,19 +706,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1605.8</c:v>
+                  <c:v>1084</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1609.2</c:v>
+                  <c:v>1188</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1314.4</c:v>
+                  <c:v>1274.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1658.4</c:v>
+                  <c:v>1147.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>950.6</c:v>
+                  <c:v>560</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -721,7 +739,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 0.05</c:v>
+                  <c:v>Deep Multilevel, ε = 50</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -787,19 +805,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1483.8</c:v>
+                  <c:v>1023.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1549.8</c:v>
+                  <c:v>1167.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1349.2</c:v>
+                  <c:v>1200.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1613.2</c:v>
+                  <c:v>1092.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>991.2</c:v>
+                  <c:v>529.20000000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1762,7 +1780,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1822,19 +1840,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-0.21688390421339804</c:v>
+                  <c:v>0.17853895119733246</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.21743077621425336</c:v>
+                  <c:v>0.10122560145256465</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.0566318926974598E-2</c:v>
+                  <c:v>5.0223546944858491E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.24579326923076925</c:v>
+                  <c:v>0.13822115384615385</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.26639913566908469</c:v>
+                  <c:v>0.5678345423676493</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1855,7 +1873,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 50</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1915,19 +1933,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-0.12443164595331924</c:v>
+                  <c:v>0.2243103970900272</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.17249205628688152</c:v>
+                  <c:v>0.11696171886820995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.3651266766021203E-3</c:v>
+                  <c:v>0.1055141579731743</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.21183894230769229</c:v>
+                  <c:v>0.17953725961538461</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.23506713999073925</c:v>
+                  <c:v>0.59160364253742859</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2111,7 +2129,7 @@
                   <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
                     <a:effectLst/>
                   </a:rPr>
-                  <a:t>Percentage of Decline</a:t>
+                  <a:t>Percentage of Improvement</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US" sz="1400">
                   <a:effectLst/>
@@ -2557,7 +2575,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2656,7 +2674,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 50</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4651,7 +4669,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4744,7 +4762,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 50</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10215,37 +10233,38 @@
     <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11">
-        <v>108184312531</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="16" t="s">
+      <c r="D1" s="11"/>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="15" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:9" ht="30">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" ht="30">
       <c r="A4" s="5"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -10269,10 +10288,10 @@
         <v>23</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -10295,13 +10314,13 @@
         <v>1353</v>
       </c>
       <c r="H5">
-        <v>1091</v>
+        <v>972</v>
       </c>
       <c r="I5">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -10324,13 +10343,13 @@
         <v>1300</v>
       </c>
       <c r="H6">
-        <v>1805</v>
+        <v>1073</v>
       </c>
       <c r="I6">
-        <v>1844</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -10353,13 +10372,13 @@
         <v>1335</v>
       </c>
       <c r="H7">
-        <v>1974</v>
+        <v>1122</v>
       </c>
       <c r="I7">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -10382,13 +10401,13 @@
         <v>1346</v>
       </c>
       <c r="H8">
-        <v>1981</v>
+        <v>1081</v>
       </c>
       <c r="I8">
-        <v>1458</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -10411,41 +10430,47 @@
         <v>1264</v>
       </c>
       <c r="H9">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="I9">
-        <v>1464</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="L13" s="13"/>
+    </row>
+    <row r="14" spans="1:12">
       <c r="C14" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="12">
         <v>447313219153</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="16" t="s">
+      <c r="E14" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="15" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
     </row>
     <row r="17" spans="1:9" ht="30">
       <c r="A17" s="5"/>
@@ -10471,7 +10496,7 @@
         <v>23</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -10497,10 +10522,10 @@
         <v>1338</v>
       </c>
       <c r="H18">
-        <v>1657</v>
+        <v>1156</v>
       </c>
       <c r="I18">
-        <v>1402</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -10526,10 +10551,10 @@
         <v>1262</v>
       </c>
       <c r="H19">
-        <v>1988</v>
+        <v>1211</v>
       </c>
       <c r="I19">
-        <v>1735</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -10555,10 +10580,10 @@
         <v>1334</v>
       </c>
       <c r="H20">
-        <v>1572</v>
+        <v>1212</v>
       </c>
       <c r="I20">
-        <v>1688</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -10584,10 +10609,10 @@
         <v>1261</v>
       </c>
       <c r="H21">
-        <v>1413</v>
+        <v>1181</v>
       </c>
       <c r="I21">
-        <v>1511</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -10613,10 +10638,10 @@
         <v>1414</v>
       </c>
       <c r="H22">
-        <v>1416</v>
+        <v>1180</v>
       </c>
       <c r="I22">
-        <v>1413</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -10628,26 +10653,26 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:9" ht="30">
       <c r="A30" s="5"/>
@@ -10673,7 +10698,7 @@
         <v>23</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -10699,10 +10724,10 @@
         <v>1257</v>
       </c>
       <c r="H31">
-        <v>1324</v>
+        <v>1263</v>
       </c>
       <c r="I31">
-        <v>1346</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -10728,10 +10753,10 @@
         <v>1373</v>
       </c>
       <c r="H32">
-        <v>1325</v>
+        <v>1283</v>
       </c>
       <c r="I32">
-        <v>1386</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -10757,10 +10782,10 @@
         <v>1271</v>
       </c>
       <c r="H33">
-        <v>1329</v>
+        <v>1276</v>
       </c>
       <c r="I33">
-        <v>1310</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -10786,10 +10811,10 @@
         <v>1396</v>
       </c>
       <c r="H34">
-        <v>1325</v>
+        <v>1255</v>
       </c>
       <c r="I34">
-        <v>1284</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -10815,10 +10840,10 @@
         <v>1413</v>
       </c>
       <c r="H35">
-        <v>1269</v>
+        <v>1296</v>
       </c>
       <c r="I35">
-        <v>1420</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -10830,26 +10855,26 @@
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" spans="1:9" ht="30">
       <c r="A43" s="5"/>
@@ -10875,7 +10900,7 @@
         <v>23</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -10901,10 +10926,10 @@
         <v>1410</v>
       </c>
       <c r="H44">
-        <v>1715</v>
+        <v>1148</v>
       </c>
       <c r="I44">
-        <v>1714</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -10930,10 +10955,10 @@
         <v>1282</v>
       </c>
       <c r="H45">
-        <v>1997</v>
+        <v>1072</v>
       </c>
       <c r="I45">
-        <v>1600</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -10959,10 +10984,10 @@
         <v>1312</v>
       </c>
       <c r="H46">
-        <v>1712</v>
+        <v>1302</v>
       </c>
       <c r="I46">
-        <v>1807</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -10988,10 +11013,10 @@
         <v>1274</v>
       </c>
       <c r="H47">
-        <v>1479</v>
+        <v>1048</v>
       </c>
       <c r="I47">
-        <v>1315</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -11017,16 +11042,16 @@
         <v>1378</v>
       </c>
       <c r="H48">
-        <v>1389</v>
+        <v>1166</v>
       </c>
       <c r="I48">
-        <v>1630</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="E50">
         <f>AVERAGE(H31:H35)</f>
-        <v>1314.4</v>
+        <v>1274.5999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -11038,26 +11063,26 @@
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
     </row>
     <row r="56" spans="1:9" ht="30">
       <c r="A56" s="5"/>
@@ -11083,7 +11108,7 @@
         <v>23</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -11109,10 +11134,10 @@
         <v>1265</v>
       </c>
       <c r="H57">
-        <v>772</v>
+        <v>585</v>
       </c>
       <c r="I57">
-        <v>1069</v>
+        <v>518</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -11138,10 +11163,10 @@
         <v>1279</v>
       </c>
       <c r="H58">
-        <v>708</v>
+        <v>519</v>
       </c>
       <c r="I58">
-        <v>1077</v>
+        <v>505</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -11167,10 +11192,10 @@
         <v>1325</v>
       </c>
       <c r="H59">
-        <v>1460</v>
+        <v>529</v>
       </c>
       <c r="I59">
-        <v>1111</v>
+        <v>546</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -11196,10 +11221,10 @@
         <v>1333</v>
       </c>
       <c r="H60">
-        <v>978</v>
+        <v>561</v>
       </c>
       <c r="I60">
-        <v>828</v>
+        <v>523</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -11225,10 +11250,10 @@
         <v>1277</v>
       </c>
       <c r="H61">
-        <v>835</v>
+        <v>606</v>
       </c>
       <c r="I61">
-        <v>871</v>
+        <v>554</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -11266,7 +11291,7 @@
         <v>23</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -11299,11 +11324,11 @@
       </c>
       <c r="H73">
         <f>AVERAGE(H5:H9)</f>
-        <v>1605.8</v>
+        <v>1084</v>
       </c>
       <c r="I73">
         <f>AVERAGE(I5:I9)</f>
-        <v>1483.8</v>
+        <v>1023.6</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -11336,11 +11361,11 @@
       </c>
       <c r="H74">
         <f>AVERAGE(H18:H22)</f>
-        <v>1609.2</v>
+        <v>1188</v>
       </c>
       <c r="I74">
         <f>AVERAGE(I18:I22)</f>
-        <v>1549.8</v>
+        <v>1167.2</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -11373,11 +11398,11 @@
       </c>
       <c r="H75">
         <f>AVERAGE(H31:H35)</f>
-        <v>1314.4</v>
+        <v>1274.5999999999999</v>
       </c>
       <c r="I75">
         <f>AVERAGE(I31:I35)</f>
-        <v>1349.2</v>
+        <v>1200.4000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -11410,11 +11435,11 @@
       </c>
       <c r="H76">
         <f>AVERAGE(H44:H48)</f>
-        <v>1658.4</v>
+        <v>1147.2</v>
       </c>
       <c r="I76">
         <f>AVERAGE(I44:I48)</f>
-        <v>1613.2</v>
+        <v>1092.2</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -11447,11 +11472,11 @@
       </c>
       <c r="H77">
         <f>AVERAGE(H57:H61)</f>
-        <v>950.6</v>
+        <v>560</v>
       </c>
       <c r="I77">
         <f>AVERAGE(I57:I61)</f>
-        <v>991.2</v>
+        <v>529.20000000000005</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -11463,130 +11488,130 @@
         <v>0</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N80" s="10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="10:14">
       <c r="J81" s="2">
         <v>0.7</v>
       </c>
-      <c r="K81" s="22">
+      <c r="K81" s="15">
         <f>(G73 - F73) / G73</f>
         <v>-0.12609881782358298</v>
       </c>
-      <c r="L81" s="22">
+      <c r="L81" s="15">
         <f>(G73 - G73) / G73</f>
         <v>0</v>
       </c>
-      <c r="M81" s="22">
+      <c r="M81" s="15">
         <f>(G73 - H73) / G73</f>
-        <v>-0.21688390421339804</v>
-      </c>
-      <c r="N81" s="22">
+        <v>0.17853895119733246</v>
+      </c>
+      <c r="N81" s="15">
         <f>(G73 - I73) / G73</f>
-        <v>-0.12443164595331924</v>
+        <v>0.2243103970900272</v>
       </c>
     </row>
     <row r="82" spans="10:14">
       <c r="J82" s="3">
         <v>0.3</v>
       </c>
-      <c r="K82" s="22">
+      <c r="K82" s="15">
         <f t="shared" ref="K82:K85" si="5">(G74 - F74) / G74</f>
         <v>-0.12165229232864273</v>
       </c>
-      <c r="L82" s="22">
+      <c r="L82" s="15">
         <f t="shared" ref="L82:L85" si="6">(G74 - G74) / G74</f>
         <v>0</v>
       </c>
-      <c r="M82" s="22">
+      <c r="M82" s="15">
         <f t="shared" ref="M82:M85" si="7">(G74 - H74) / G74</f>
-        <v>-0.21743077621425336</v>
-      </c>
-      <c r="N82" s="22">
+        <v>0.10122560145256465</v>
+      </c>
+      <c r="N82" s="15">
         <f t="shared" ref="N82:N85" si="8">(G74 - I74) / G74</f>
-        <v>-0.17249205628688152</v>
+        <v>0.11696171886820995</v>
       </c>
     </row>
     <row r="83" spans="10:14">
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="22">
-        <f t="shared" si="5"/>
+      <c r="K83" s="15">
+        <f>(G75 - F75) / G75</f>
         <v>-7.7347242921013373E-2</v>
       </c>
-      <c r="L83" s="22">
+      <c r="L83" s="15">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M83" s="22">
+      <c r="M83" s="15">
         <f t="shared" si="7"/>
-        <v>2.0566318926974598E-2</v>
-      </c>
-      <c r="N83" s="22">
+        <v>5.0223546944858491E-2</v>
+      </c>
+      <c r="N83" s="15">
         <f t="shared" si="8"/>
-        <v>-5.3651266766021203E-3</v>
+        <v>0.1055141579731743</v>
       </c>
     </row>
     <row r="84" spans="10:14">
       <c r="J84" s="3">
         <v>-0.3</v>
       </c>
-      <c r="K84" s="22">
+      <c r="K84" s="15">
         <f t="shared" si="5"/>
         <v>-7.1514423076923114E-2</v>
       </c>
-      <c r="L84" s="22">
+      <c r="L84" s="15">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M84" s="22">
+      <c r="M84" s="15">
         <f t="shared" si="7"/>
-        <v>-0.24579326923076925</v>
-      </c>
-      <c r="N84" s="22">
+        <v>0.13822115384615385</v>
+      </c>
+      <c r="N84" s="15">
         <f t="shared" si="8"/>
-        <v>-0.21183894230769229</v>
+        <v>0.17953725961538461</v>
       </c>
     </row>
     <row r="85" spans="10:14">
       <c r="J85" s="3">
         <v>-0.7</v>
       </c>
-      <c r="K85" s="22">
+      <c r="K85" s="15">
         <f t="shared" si="5"/>
         <v>-0.15341873745948445</v>
       </c>
-      <c r="L85" s="22">
+      <c r="L85" s="15">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M85" s="22">
+      <c r="M85" s="15">
         <f t="shared" si="7"/>
-        <v>0.26639913566908469</v>
-      </c>
-      <c r="N85" s="22">
+        <v>0.5678345423676493</v>
+      </c>
+      <c r="N85" s="15">
         <f t="shared" si="8"/>
-        <v>0.23506713999073925</v>
+        <v>0.59160364253742859</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A55:G55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11607,26 +11632,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:9" ht="60">
       <c r="A3" s="7"/>
@@ -11801,26 +11826,26 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="60">
       <c r="A15" s="7"/>
@@ -11995,26 +12020,26 @@
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="60">
       <c r="A26" s="7"/>
@@ -12189,26 +12214,26 @@
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="20"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="60">
       <c r="A37" s="7"/>
@@ -12383,26 +12408,26 @@
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="20"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="22"/>
     </row>
     <row r="49" spans="1:9" ht="60">
       <c r="A49" s="7"/>
@@ -12608,10 +12633,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -12801,17 +12826,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A48:G48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12833,26 +12858,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:9" ht="45">
       <c r="A3" s="5"/>
@@ -13000,11 +13025,11 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" spans="1:9">
       <c r="B11" s="1" t="s">
@@ -13106,26 +13131,26 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:9" ht="45">
       <c r="A23" s="5"/>
@@ -13270,11 +13295,11 @@
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="1" t="s">
@@ -13376,26 +13401,26 @@
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
     </row>
     <row r="42" spans="1:9" ht="45">
       <c r="A42" s="5"/>
@@ -13540,11 +13565,11 @@
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
     </row>
     <row r="50" spans="1:9">
       <c r="B50" s="1" t="s">
@@ -13646,26 +13671,26 @@
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
     </row>
     <row r="61" spans="1:9" ht="45">
       <c r="A61" s="5"/>
@@ -13828,11 +13853,11 @@
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
     </row>
     <row r="69" spans="1:9">
       <c r="B69" s="1" t="s">
@@ -13952,26 +13977,26 @@
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
     </row>
     <row r="80" spans="1:9" ht="45">
       <c r="A80" s="5"/>
@@ -14146,11 +14171,11 @@
       </c>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" s="21" t="s">
+      <c r="A87" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B87" s="21"/>
-      <c r="C87" s="21"/>
+      <c r="B87" s="23"/>
+      <c r="C87" s="23"/>
     </row>
     <row r="88" spans="1:9">
       <c r="B88" s="1" t="s">
@@ -14281,15 +14306,15 @@
       <c r="G99" s="17"/>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="15" t="s">
+      <c r="A100" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B100" s="15"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="19"/>
+      <c r="D100" s="19"/>
+      <c r="E100" s="19"/>
+      <c r="F100" s="19"/>
+      <c r="G100" s="19"/>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="8"/>
@@ -14300,25 +14325,25 @@
         <v>0</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E101" s="23" t="s">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
         <v>0.7</v>
       </c>
-      <c r="B102" s="22">
+      <c r="B102" s="15">
         <f>AVERAGE(F4:F8)</f>
         <v>0.49180000000000001</v>
       </c>
-      <c r="C102" s="22">
+      <c r="C102" s="15">
         <f>AVERAGE(G4:G8)</f>
         <v>0.48280000000000001</v>
       </c>
-      <c r="D102" s="22">
+      <c r="D102" s="15">
         <f>AVERAGE(H4:H8)</f>
         <v>1.7649999999999999E-3</v>
       </c>
@@ -14331,19 +14356,19 @@
       <c r="A103" s="3">
         <v>0.3</v>
       </c>
-      <c r="B103" s="22">
+      <c r="B103" s="15">
         <f>AVERAGE(F24:F28)</f>
         <v>0.26040000000000002</v>
       </c>
-      <c r="C103" s="22">
+      <c r="C103" s="15">
         <f>AVERAGE(G24:G28)</f>
         <v>0.26240000000000008</v>
       </c>
-      <c r="D103" s="22">
+      <c r="D103" s="15">
         <f>AVERAGE(H24:H28)</f>
         <v>0</v>
       </c>
-      <c r="E103" s="22">
+      <c r="E103" s="15">
         <f>AVERAGE(I24:I28)</f>
         <v>3.7926000000000001E-2</v>
       </c>
@@ -14352,19 +14377,19 @@
       <c r="A104" s="3">
         <v>0</v>
       </c>
-      <c r="B104" s="22">
+      <c r="B104" s="15">
         <f>AVERAGE(F43:F47)</f>
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="C104" s="22">
+      <c r="C104" s="15">
         <f>AVERAGE(G43:G47)</f>
         <v>2.8080000000000001E-2</v>
       </c>
-      <c r="D104" s="22">
+      <c r="D104" s="15">
         <f>AVERAGE(H43:H47)</f>
         <v>0</v>
       </c>
-      <c r="E104" s="22">
+      <c r="E104" s="15">
         <f>AVERAGE(I43:I47)</f>
         <v>2.1520000000000001E-2</v>
       </c>
@@ -14373,19 +14398,19 @@
       <c r="A105" s="3">
         <v>-0.3</v>
       </c>
-      <c r="B105" s="22">
+      <c r="B105" s="15">
         <f>AVERAGE(F62:F66)</f>
         <v>0.34408000000000005</v>
       </c>
-      <c r="C105" s="22">
+      <c r="C105" s="15">
         <f>AVERAGE(G62:G66)</f>
         <v>0.33877999999999997</v>
       </c>
-      <c r="D105" s="22">
+      <c r="D105" s="15">
         <f>AVERAGE(H62:H66)</f>
         <v>0</v>
       </c>
-      <c r="E105" s="22">
+      <c r="E105" s="15">
         <f>AVERAGE(I62:I66)</f>
         <v>3.4943599999999998E-2</v>
       </c>
@@ -14394,32 +14419,32 @@
       <c r="A106" s="3">
         <v>-0.7</v>
       </c>
-      <c r="B106" s="22">
+      <c r="B106" s="15">
         <f>AVERAGE(F81:F85)</f>
         <v>0.90340000000000009</v>
       </c>
-      <c r="C106" s="22">
+      <c r="C106" s="15">
         <f>AVERAGE(G81:G85)</f>
         <v>0.8972</v>
       </c>
-      <c r="D106" s="22">
+      <c r="D106" s="15">
         <f>AVERAGE(H81:H85)</f>
         <v>0</v>
       </c>
-      <c r="E106" s="22">
+      <c r="E106" s="15">
         <f>AVERAGE(I81:I85)</f>
         <v>1.3763999999999998E-2</v>
       </c>
     </row>
     <row r="107" spans="1:7">
-      <c r="D107" s="22"/>
+      <c r="D107" s="15"/>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="21" t="s">
+      <c r="A110" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B110" s="21"/>
-      <c r="C110" s="21"/>
+      <c r="B110" s="23"/>
+      <c r="C110" s="23"/>
     </row>
     <row r="111" spans="1:7">
       <c r="B111" s="1" t="s">
@@ -14561,6 +14586,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A99:G99"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A110:C110"/>
@@ -14574,11 +14604,6 @@
     <mergeCell ref="A78:G78"/>
     <mergeCell ref="A79:G79"/>
     <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14601,26 +14626,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:9" ht="75">
       <c r="A3" s="7"/>
@@ -14795,26 +14820,26 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="75">
       <c r="A15" s="7"/>
@@ -14989,26 +15014,26 @@
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="75">
       <c r="A26" s="7"/>
@@ -15183,26 +15208,26 @@
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="22"/>
     </row>
     <row r="38" spans="1:9" ht="75">
       <c r="A38" s="7"/>
@@ -15377,26 +15402,26 @@
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="20"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="22"/>
     </row>
     <row r="50" spans="1:9" ht="75">
       <c r="A50" s="7"/>
@@ -15582,15 +15607,15 @@
       <c r="G59" s="17"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="20"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="22"/>
     </row>
     <row r="61" spans="1:9" ht="75">
       <c r="A61" s="8"/>
@@ -15806,18 +15831,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A60:G60"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A48:G48"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Experiments data/Cardinality Skewness/Skewness_email_Graph.xlsx
+++ b/Experiments data/Cardinality Skewness/Skewness_email_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Cardinality Skewness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9284ECC-9D6B-4823-9810-82B7420064B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB2827D-3182-477F-BC48-FBE0761A4333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -134,10 +134,10 @@
     <t>Deep Multilevel, ε = 10</t>
   </si>
   <si>
-    <t>Deep NUGP, ε = 50</t>
+    <t>Deep NUGP, ε= 0</t>
   </si>
   <si>
-    <t>Deep NUGP, ε= 0</t>
+    <t>Deep NUGP, ε relaxed</t>
   </si>
 </sst>
 </file>
@@ -331,13 +331,13 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1545,7 +1545,7 @@
                   </a:sysClr>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Edge Cut with Different Skewness Values</a:t>
+              <a:t>Edge Cut with Different Partition Skenewss</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1873,7 +1873,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 50</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1996,7 +1996,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2009,7 +2009,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:rPr lang="en-US" sz="1800"/>
                   <a:t>Skewness Value</a:t>
                 </a:r>
               </a:p>
@@ -2028,7 +2028,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2113,7 +2113,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2126,12 +2126,12 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
+                  <a:rPr lang="en-US" sz="1600" b="0" i="0" baseline="0">
                     <a:effectLst/>
                   </a:rPr>
                   <a:t>Percentage of Improvement</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US" sz="1400">
+                <a:endParaRPr lang="en-US" sz="1600">
                   <a:effectLst/>
                 </a:endParaRPr>
               </a:p>
@@ -2141,8 +2141,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="1.705863755549724E-2"/>
-              <c:y val="0.34590281123442446"/>
+              <c:x val="1.7058644230875164E-2"/>
+              <c:y val="0.21576760650935678"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2158,7 +2158,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2340,7 +2340,7 @@
                   </a:sysClr>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Run Time with Different Skewness</a:t>
+              <a:t>Runtime with Different Skewness</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2674,7 +2674,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 50</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4762,7 +4762,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 50</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10254,15 +10254,15 @@
       <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:12" ht="30">
       <c r="A4" s="5"/>
@@ -10462,15 +10462,15 @@
       <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
     </row>
     <row r="17" spans="1:9" ht="30">
       <c r="A17" s="5"/>
@@ -10664,15 +10664,15 @@
       <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
     </row>
     <row r="30" spans="1:9" ht="30">
       <c r="A30" s="5"/>
@@ -10866,15 +10866,15 @@
       <c r="G41" s="18"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
     </row>
     <row r="43" spans="1:9" ht="30">
       <c r="A43" s="5"/>
@@ -11074,15 +11074,15 @@
       <c r="G54" s="18"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="19" t="s">
+      <c r="A55" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
     </row>
     <row r="56" spans="1:9" ht="30">
       <c r="A56" s="5"/>
@@ -11257,15 +11257,15 @@
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
     </row>
     <row r="72" spans="1:14" ht="30">
       <c r="A72" s="5"/>
@@ -11488,10 +11488,10 @@
         <v>0</v>
       </c>
       <c r="M80" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N80" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="N80" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="81" spans="10:14">
@@ -11601,17 +11601,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A55:G55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12602,15 +12602,15 @@
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
     </row>
     <row r="60" spans="1:9" ht="60">
       <c r="A60" s="5"/>
@@ -12633,10 +12633,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I60" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="I60" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -12826,17 +12826,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A48:G48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12869,15 +12869,15 @@
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="45">
       <c r="A3" s="5"/>
@@ -13142,15 +13142,15 @@
       <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" spans="1:9" ht="45">
       <c r="A23" s="5"/>
@@ -13412,15 +13412,15 @@
       <c r="G40" s="18"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
     </row>
     <row r="42" spans="1:9" ht="45">
       <c r="A42" s="5"/>
@@ -13682,15 +13682,15 @@
       <c r="G59" s="18"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="19" t="s">
+      <c r="A60" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
     </row>
     <row r="61" spans="1:9" ht="45">
       <c r="A61" s="5"/>
@@ -13988,15 +13988,15 @@
       <c r="G78" s="18"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="19" t="s">
+      <c r="A79" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="19"/>
-      <c r="G79" s="19"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
     </row>
     <row r="80" spans="1:9" ht="45">
       <c r="A80" s="5"/>
@@ -14295,26 +14295,26 @@
       </c>
     </row>
     <row r="99" spans="1:7">
-      <c r="A99" s="17" t="s">
+      <c r="A99" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B99" s="17"/>
-      <c r="C99" s="17"/>
-      <c r="D99" s="17"/>
-      <c r="E99" s="17"/>
-      <c r="F99" s="17"/>
-      <c r="G99" s="17"/>
+      <c r="B99" s="19"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="19"/>
+      <c r="E99" s="19"/>
+      <c r="F99" s="19"/>
+      <c r="G99" s="19"/>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="19" t="s">
+      <c r="A100" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19"/>
-      <c r="G100" s="19"/>
+      <c r="B100" s="17"/>
+      <c r="C100" s="17"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="17"/>
+      <c r="F100" s="17"/>
+      <c r="G100" s="17"/>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="8"/>
@@ -14325,10 +14325,10 @@
         <v>0</v>
       </c>
       <c r="D101" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E101" s="16" t="s">
         <v>33</v>
-      </c>
-      <c r="E101" s="16" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -14586,11 +14586,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A99:G99"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A110:C110"/>
@@ -14604,6 +14599,11 @@
     <mergeCell ref="A78:G78"/>
     <mergeCell ref="A79:G79"/>
     <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15596,15 +15596,15 @@
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="20" t="s">
@@ -15831,18 +15831,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A49:G49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Experiments data/Cardinality Skewness/Skewness_email_Graph.xlsx
+++ b/Experiments data/Cardinality Skewness/Skewness_email_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Cardinality Skewness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9284ECC-9D6B-4823-9810-82B7420064B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1185D353-1E24-4263-B11E-304D44D891D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -4821,7 +4821,7 @@
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
-                <c:pt idx="0" formatCode="General">
+                <c:pt idx="0" formatCode="0.00%">
                   <c:v>0.15404000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -10231,6 +10231,10 @@
     <col min="5" max="5" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -14347,7 +14351,7 @@
         <f>AVERAGE(H4:H8)</f>
         <v>1.7649999999999999E-3</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="4">
         <f>AVERAGE(I4:I8)</f>
         <v>0.15404000000000001</v>
       </c>
